--- a/src/attributions/attributions_ig_traj_469.xlsx
+++ b/src/attributions/attributions_ig_traj_469.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2690090356215627</v>
+        <v>0.05765515933198757</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.02637554088426717</v>
+        <v>-0.0266983767872717</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1123383354557997</v>
+        <v>-0.0212158617798364</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3206001098124467</v>
+        <v>0.1391512176532301</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.06308260878671244</v>
+        <v>-0.06953295742781898</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.2241744423607865</v>
+        <v>-0.03052122077212679</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1129548185232716</v>
+        <v>0.01776730591050792</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,88 +1065,88 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.007135033394147983</v>
+        <v>-0.03542056640738029</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.03623904984095647</v>
+        <v>-0.008918865599046701</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1030346890673349</v>
+        <v>-0.03963921130504037</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1080479373519222</v>
+        <v>-0.05572515483073788</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.02482966677512236</v>
+        <v>0.02169105850186929</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.06240129674679108</v>
+        <v>0.02576300364073627</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.06569997225691067</v>
+        <v>-0.004733610379846995</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.04415961339280109</v>
+        <v>0.000896628972176819</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4641554599921712</v>
+        <v>0.1601026297524362</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1835073805560317</v>
+        <v>-0.0321356227801405</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.1264633796800418</v>
+        <v>-0.004003151308929205</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.02134976217451304</v>
+        <v>-0.01272292900378514</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.06689558345129387</v>
+        <v>-0.02586979115060976</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,109 +1182,109 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.09391921776469778</v>
+        <v>-0.02846597834920692</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.006476634408454984</v>
+        <v>0.02472485686200142</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.2371793715031392</v>
+        <v>0.06670961401210343</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.05467576975080499</v>
+        <v>0.02591708819752604</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2722343885733226</v>
+        <v>0.0806140966418936</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.02834383154614473</v>
+        <v>-0.0295524267579333</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0.01288832257468495</v>
+        <v>-0.02313249184552403</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1051462076830022</v>
+        <v>-0.03475633574966971</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.003534433938428292</v>
+        <v>0.01551454895116017</v>
       </c>
       <c r="CI2" t="n">
         <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.08455035391483008</v>
+        <v>0.02026114686007841</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.0256699323857791</v>
+        <v>-0.04505303582567504</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.06898804015887712</v>
+        <v>0.00847941776326358</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,67 +1293,67 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0.008830447320033496</v>
+        <v>0.01770997543966984</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.1081027698394665</v>
+        <v>-0.03532905653528787</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.00522312759173923</v>
+        <v>0.007452648158810973</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.05825408263053589</v>
+        <v>0.02278946176620756</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1476767009123628</v>
+        <v>-0.06740358645322757</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08503129823391828</v>
+        <v>-0.0005437695397151852</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.04289698329109538</v>
+        <v>0.001252663187728241</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.03075852568812498</v>
+        <v>-0.01655125345828333</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,25 +1362,25 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.06001691410144295</v>
+        <v>0.02327270414025818</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.02413756164726932</v>
+        <v>0.02567941216524706</v>
       </c>
       <c r="DW2" t="n">
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1996332817378985</v>
+        <v>-0.01917717437936465</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.0008513228680456251</v>
+        <v>-0.02428652856531025</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,22 +1401,22 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.02326533694814667</v>
+        <v>0.001929117663526941</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.05250484643517359</v>
+        <v>-0.02296937592475216</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.04512827807598933</v>
+        <v>-0.009919481382258795</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,70 +1425,70 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.1222390620336054</v>
+        <v>0.01433146022394076</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.0583947550744899</v>
+        <v>-0.01585453153299899</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.0355166459155681</v>
+        <v>0.02152494758020031</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.05409069200646025</v>
+        <v>0.02805836881879937</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.1144069312974093</v>
+        <v>-0.04849610643041793</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.001491313125920189</v>
+        <v>0.007449756962177627</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.05586383080367818</v>
+        <v>0.01969648461422418</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.01562846512879318</v>
+        <v>0.03551436274796554</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,25 +1497,25 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.05347959775200992</v>
+        <v>-0.003239777655372067</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.007900361801987587</v>
+        <v>0.03585285026385007</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.003235808986746197</v>
+        <v>-0.01060017193994352</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
@@ -1524,25 +1524,25 @@
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.01402584999415574</v>
+        <v>0.009397492419316115</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.04078279203365184</v>
+        <v>0.002803624219108015</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.08470893706531565</v>
+        <v>-0.02366953528934799</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1563,7 +1563,7 @@
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.04196394480333632</v>
+        <v>-0.01219221169216842</v>
       </c>
     </row>
     <row r="3">
@@ -2706,25 +2706,25 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1737140760692959</v>
+        <v>0.004236942225626563</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01884553871126724</v>
+        <v>-0.001510725964859576</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1582922978418645</v>
+        <v>-0.00239697640283136</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1806129855554133</v>
+        <v>0.01066461551710592</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,16 +2745,16 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02794389860530046</v>
+        <v>-0.002749382384587497</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2082750794941135</v>
+        <v>-0.006370167069205295</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2763,61 +2763,61 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09090449934639262</v>
+        <v>-0.0005363076840573068</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2093959071977421</v>
+        <v>-0.003439541967412121</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1149997161091573</v>
+        <v>0.0002792530852372387</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1366696514026354</v>
+        <v>-0.002650765547674125</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.07029635191886457</v>
+        <v>-0.00487903579000852</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.04621653821806405</v>
+        <v>-4.062074885570771e-05</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.01564571025880914</v>
+        <v>-0.0002308049646415497</v>
       </c>
       <c r="AM5" t="n">
         <v>-0</v>
@@ -2826,25 +2826,25 @@
         <v>-0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0232933327149728</v>
+        <v>-0.0003903415417867219</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.04254466202878743</v>
+        <v>0.0002642966170467154</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.2521967869046079</v>
+        <v>0.0103622951938541</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
@@ -2853,13 +2853,13 @@
         <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1003878025029373</v>
+        <v>-3.975462062929253e-05</v>
       </c>
       <c r="AY5" t="n">
         <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.2383136482257326</v>
+        <v>-0.0003937757765848502</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2868,10 +2868,10 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0387817606377686</v>
+        <v>-0.001604026933949225</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02190229594871177</v>
+        <v>-0.001648359597931271</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.03739635802762917</v>
+        <v>-0.0003508500771968924</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2898,22 +2898,22 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01355176047936952</v>
+        <v>0.001908873974926926</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1732292063443753</v>
+        <v>0.005702363905216046</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.06729305073319519</v>
+        <v>-0.000491522496389621</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,52 +2922,52 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.09827352685187418</v>
+        <v>0.005111705851033388</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1098682902855702</v>
+        <v>-0.0004286119716496358</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.1424800481727548</v>
+        <v>-0.001213101985957372</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.07193390622760323</v>
+        <v>-0.001609515335391958</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.03890901710456447</v>
+        <v>0.00113757773061618</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.05450850098507287</v>
+        <v>0.0008663085583165222</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
@@ -2976,25 +2976,25 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.06830904595844711</v>
+        <v>-0.002143972620245902</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.0423383557637665</v>
+        <v>0.0003664808027909204</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.04333254231908479</v>
+        <v>-0.002039193468339932</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
@@ -3003,25 +3003,25 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.04886765219026017</v>
+        <v>-0.001833181772580364</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.02064303465692164</v>
+        <v>0.0005813366612017178</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.05828837948056111</v>
+        <v>0.001361763308435163</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.073832851750888</v>
+        <v>-0.001127744802459624</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0245034813039324</v>
+        <v>-0.003793517098776549</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.04220620785160419</v>
+        <v>0.0009356139097622458</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.03453433118261568</v>
+        <v>0.0005822894505294162</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -3069,40 +3069,40 @@
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02431388384833857</v>
+        <v>-5.351655815875155e-06</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.008177560258946694</v>
+        <v>0.002011592224837301</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1710106070484918</v>
+        <v>-0.001376419611923334</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
         <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.0181208874306336</v>
+        <v>-0.0008423754941276835</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.03975461134503491</v>
+        <v>0.003034259782838591</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3114,76 +3114,76 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.01965983724005753</v>
+        <v>-0.001085650877441044</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.03866789182557661</v>
+        <v>0.0007875302810836546</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.06226573666274811</v>
+        <v>-0.0002566023568291715</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.03566006645165865</v>
+        <v>-0.001065907782973921</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02222437283756182</v>
+        <v>-0.0002341735990294964</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.01025780059560935</v>
+        <v>0.0002236672614325686</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.06602333382210977</v>
+        <v>-0.002356011170080764</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.03506151650410121</v>
+        <v>0.000341209589580499</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.04863729690093081</v>
+        <v>0.0009463737480580146</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,52 +3192,52 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.07151901014542787</v>
+        <v>0.002327600666705858</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.004260822048312872</v>
+        <v>-0.001871032179519452</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.03852305282167397</v>
+        <v>-0.0016556954015152</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
         <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.0107065682687198</v>
+        <v>-0.0001644108910088839</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.005767455097152811</v>
+        <v>0.0003093637897736256</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.03505784616239327</v>
+        <v>0.001668880187458135</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
@@ -3246,10 +3246,10 @@
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.08655565127134791</v>
+        <v>-0.001025132796422012</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3258,13 +3258,13 @@
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.1806407828432866</v>
+        <v>0.00244852221377348</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
@@ -3847,25 +3847,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4455760629490914</v>
+        <v>0.3488694955733931</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3041085984013</v>
+        <v>-0.3539976126215166</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.006743610329542356</v>
+        <v>0.03203891781531605</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3874,22 +3874,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4152576574293815</v>
+        <v>0.4887246337858229</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3387821473359149</v>
+        <v>-0.4378701850645553</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06318291834382236</v>
+        <v>-0.006356753693472714</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3898,25 +3898,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1769845436126745</v>
+        <v>0.2068364855318356</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01083885226992642</v>
+        <v>-0.03663901811389404</v>
       </c>
       <c r="W7" t="n">
-        <v>0.143459926637666</v>
+        <v>-0.03324823373259628</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,73 +3925,73 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1377179051384124</v>
+        <v>-0.1470829511427163</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>9.151885110612083e-05</v>
+        <v>-0.2005211643078019</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.02522275758571156</v>
+        <v>-0.1675159763810496</v>
       </c>
       <c r="AG7" t="n">
         <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.007000445865510865</v>
+        <v>0.2441891034325429</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1149991503188726</v>
+        <v>-0.08969698316962139</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.07070727523694696</v>
+        <v>0.1617947871479106</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.4825420558410646</v>
+        <v>0.4235224727467694</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.06439091268294891</v>
+        <v>-0.2532425744902257</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2088440188511197</v>
+        <v>-0.1766950888729614</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4000,25 +4000,25 @@
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02719132652210001</v>
+        <v>-0.06956874442240354</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.08788290643116611</v>
+        <v>-0.1074543691744949</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1094549328530433</v>
+        <v>-0.07345001093182985</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4033,79 +4033,79 @@
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.06438024714569722</v>
+        <v>-0.1101847232742747</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.07213905901269999</v>
+        <v>0.0870622130177464</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.2050067101581966</v>
+        <v>-0.06431415016602172</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2166346105267306</v>
+        <v>0.4645495837975127</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01180077790161953</v>
+        <v>-0.1934632353360001</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1195108594480982</v>
+        <v>-0.01535121604926296</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1222616346406577</v>
+        <v>-0.136707937744972</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.03448385190292999</v>
+        <v>0.1962612695375959</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.03138691555326227</v>
+        <v>-0.04414314005699507</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,19 +4117,19 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.004231651107357583</v>
+        <v>-0.08580022817579076</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1904135015562961</v>
+        <v>0.4491746761767676</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.150745853978354</v>
+        <v>0.243594599076616</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,28 +4138,28 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1142039630352434</v>
+        <v>-0.1341703920928646</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.06982761398991796</v>
+        <v>0.2005330102156756</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02824620691059567</v>
+        <v>-0.02750304621931587</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4168,49 +4168,49 @@
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1080932701912477</v>
+        <v>-0.2494812284017769</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.005582158656292769</v>
+        <v>0.0819790929745426</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.01412072653562035</v>
+        <v>-0.1131295637206304</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.006030941702173314</v>
+        <v>-0.03785283923051218</v>
       </c>
       <c r="DP7" t="n">
         <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.1107300618665427</v>
+        <v>0.06476718941447315</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.07608414809096867</v>
+        <v>0.01269781979300709</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,76 +4225,76 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0646630914615962</v>
+        <v>-0.02228295340648015</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.007827651698988096</v>
+        <v>-0.1137898302176372</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01458587917055509</v>
+        <v>-0.113784475492489</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1185216890285587</v>
+        <v>-0.08361786288790674</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.06095883835186508</v>
+        <v>0.1540645587554189</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.07992132810813288</v>
+        <v>0.006269806300607729</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.115144652072036</v>
+        <v>-0.1563795905071236</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0662566454047982</v>
+        <v>0.1068848989449786</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.01306653633612702</v>
+        <v>-0.02074322580997785</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4303,25 +4303,25 @@
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1139927730419903</v>
+        <v>-0.1649718791239365</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.04048420147406238</v>
+        <v>0.2266813741820491</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03000399156106575</v>
+        <v>-0.04557793501135081</v>
       </c>
       <c r="FC7" t="n">
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4330,19 +4330,19 @@
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.001469546492849552</v>
+        <v>-0.1358383702054913</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1033866821379798</v>
+        <v>0.161116320906044</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.003274122916975363</v>
+        <v>0.06724482327697726</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
@@ -4354,58 +4354,58 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.004250349493744135</v>
+        <v>-0.02779087371432626</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.04487710021738089</v>
+        <v>0.04016566855916535</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.001508330873060902</v>
+        <v>0.03564727196932278</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0160400294067794</v>
+        <v>-0.2292612009669464</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.1058364420517379</v>
+        <v>0.1222741867097254</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,19 +4416,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1972020054751076</v>
+        <v>0.4744765731955602</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01558685433787569</v>
+        <v>-0.02293838323787338</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1231396370707967</v>
+        <v>-0.1892746465241175</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4443,76 +4443,76 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1861828020258288</v>
+        <v>0.8073315907748722</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0103155063492132</v>
+        <v>-0.1603733988433517</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1902560143555095</v>
+        <v>-0.3210596850346624</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02844466550133989</v>
+        <v>0.2931432064696319</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.03061289678256857</v>
+        <v>-0.1360433182586873</v>
       </c>
       <c r="X8" t="n">
-        <v>0.006854146032239612</v>
+        <v>-0.0609489495740539</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03264733313391156</v>
+        <v>0.08954957850544429</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.03382581125217318</v>
+        <v>-0.5682445846509869</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.003861624518776668</v>
+        <v>-0.2724515621473873</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4521,22 +4521,22 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01775213755335814</v>
+        <v>0.2790943135396213</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.01823899586871976</v>
+        <v>0.04552868281544636</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.04574422362505487</v>
+        <v>-0.1518876450332183</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1578527287891762</v>
+        <v>1.052668442661024</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
@@ -4560,13 +4560,13 @@
         <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.03009066623931703</v>
+        <v>-0.1791922635416892</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1060920313981854</v>
+        <v>-0.4680986486122495</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
         <v>-0</v>
@@ -4578,73 +4578,73 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0533905961460187</v>
+        <v>-0.1082840202524936</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.01875711993082825</v>
+        <v>-0.1825995468116091</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.0260917614106362</v>
+        <v>-0.01399479784929215</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0592088425318155</v>
+        <v>0.08607997164941948</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01763217451831689</v>
+        <v>0.1276575156226594</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.02108543921541977</v>
+        <v>-0.07789629854058609</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.08191780786689601</v>
+        <v>0.7061092499800377</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.007125005831504456</v>
+        <v>-0.06959575426303503</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.03847278849607353</v>
+        <v>-0.2596173471395802</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4659,7 +4659,7 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.04777368011568461</v>
+        <v>-0.2490949129492111</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
@@ -4668,52 +4668,52 @@
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.006358906338209396</v>
+        <v>0.07621755917437907</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04169059791616035</v>
+        <v>0.1406393120176551</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01786519925997607</v>
+        <v>-0.5979908009792566</v>
       </c>
       <c r="CO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.008243849787792825</v>
+        <v>0.4372844678991471</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.02700168368846984</v>
+        <v>0.3325018106959195</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.03805565230960602</v>
+        <v>-0.2245423006206138</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
@@ -4722,13 +4722,13 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.008520932015773395</v>
+        <v>0.04025140157864317</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04411783020122837</v>
+        <v>0.1408068890643731</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.04732746280423242</v>
+        <v>-0.04650510696045393</v>
       </c>
       <c r="DG8" t="n">
         <v>-0</v>
@@ -4749,16 +4749,16 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04279812006264715</v>
+        <v>-0.4270743754951312</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-0.003812255310813603</v>
+        <v>-0.03606717404025087</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
         <v>0</v>
@@ -4767,34 +4767,34 @@
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02562372354210346</v>
+        <v>-0.145431385429476</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01710577946207813</v>
+        <v>0.145750919821037</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.006448372229485514</v>
+        <v>0.02509771970809119</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02740982527823174</v>
+        <v>0.02068096742855898</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,16 +4803,16 @@
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01555094249676832</v>
+        <v>0.130912714239457</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.02523314648901329</v>
+        <v>-0.1316147039071578</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
@@ -4821,7 +4821,7 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.03550189648554335</v>
+        <v>-0.008205177124254297</v>
       </c>
       <c r="EH8" t="n">
         <v>-0</v>
@@ -4830,37 +4830,37 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.00593347913968142</v>
+        <v>-0.06028917780077989</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.02482667443196165</v>
+        <v>0.003883143648509684</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.01666830095076784</v>
+        <v>-0.03508364650094157</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.01238946730654401</v>
+        <v>-0.155368948910957</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.03271213422285889</v>
+        <v>0.06069428473449218</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
@@ -4875,91 +4875,91 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03881320182765093</v>
+        <v>-0.2537576455757214</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.003489455518116033</v>
+        <v>0.008388228344768892</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04610251647322518</v>
+        <v>0.1330263768869871</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.004145394872816544</v>
+        <v>-0.3389914667461389</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.03060528580917432</v>
+        <v>0.1876940271002804</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03346116436839619</v>
+        <v>0.1613768624640028</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.002991917923197629</v>
+        <v>-0.06000083521121608</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.002759838109073959</v>
+        <v>0.02483429309762353</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.02460694363349581</v>
+        <v>-0.009282727442028373</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01201408305352531</v>
+        <v>-0.06117225380489345</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
@@ -4968,16 +4968,16 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.03599993409051818</v>
+        <v>-0.03873927549584642</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5551,19 +5551,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8348270013532564</v>
+        <v>0.01089796440072189</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1928922286597414</v>
+        <v>-0.006977718557593932</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,25 +5572,25 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6206120684111265</v>
+        <v>-0.005211758474300362</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7261114169484564</v>
+        <v>0.01904898574401881</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.433800255898227</v>
+        <v>-0.01534313898542339</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,16 +5599,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.080460706453065</v>
+        <v>-0.01506751991448772</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3672846148023838</v>
+        <v>0.01024294798673228</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,16 +5617,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3055026661308144</v>
+        <v>-0.007296014221956534</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.2121785373081751</v>
+        <v>-0.004175981275924238</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
@@ -5635,16 +5635,16 @@
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.332517666763014</v>
+        <v>-0.008388178173709777</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.2259458599740988</v>
+        <v>-0.01177483185799811</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,34 +5653,34 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.3881449696969793</v>
+        <v>0.002988604257492058</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1215764737511556</v>
+        <v>0.006239455451455149</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01452735571944643</v>
+        <v>-0.000975649721416389</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.2011266619307084</v>
+        <v>0.0009408669387319347</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.30692550689333</v>
+        <v>0.02230669499660267</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,43 +5698,43 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.5764026283372358</v>
+        <v>-0.00144821127015388</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.07461953905174959</v>
+        <v>-0.003689067017159994</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.09980686723540562</v>
+        <v>-0.006516250897614667</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.3435565131048876</v>
+        <v>-0.01063988112071038</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.2816467346047613</v>
+        <v>-0.0008582338286923667</v>
       </c>
       <c r="BK10" t="n">
         <v>-0</v>
@@ -5743,25 +5743,25 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6843433952756947</v>
+        <v>0.008246857268706201</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.8763412875366018</v>
+        <v>0.01338914056011492</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.3526171564207326</v>
+        <v>0.006457433882212279</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,43 +5770,43 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.6232804262360672</v>
+        <v>0.01915391433977753</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.3275339370060709</v>
+        <v>-0.001715540978778228</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.005965592994580752</v>
+        <v>-0.007384436191950679</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.2315112716368397</v>
+        <v>-0.002838535184280799</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.009825684334269683</v>
+        <v>0.003163655186119755</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,16 +5815,16 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.2421564068012171</v>
+        <v>0.003624879629757678</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.6186397959429448</v>
+        <v>-0.00586796463402806</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
@@ -5833,34 +5833,34 @@
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.6665084022919777</v>
+        <v>0.00958213351233396</v>
       </c>
       <c r="CR10" t="n">
         <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0.2008247157968645</v>
+        <v>0.004217602161687544</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1833094359683755</v>
+        <v>-0.002678809280793106</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.02106584646305081</v>
+        <v>0.002881095285650261</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,52 +5869,52 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.1177904992255792</v>
+        <v>0.004897629560727179</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.7742128212636097</v>
+        <v>-0.00720585858740063</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.02791378291513351</v>
+        <v>0.002343394095859221</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.009847316689250245</v>
+        <v>-0.0003722436615402493</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.2332865393575126</v>
+        <v>-0.003208490429518682</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.08612550847129528</v>
+        <v>-0.003620955351727971</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,16 +5923,16 @@
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1884009538427947</v>
+        <v>0.001473928326758133</v>
       </c>
       <c r="DV10" t="n">
         <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.01453415761358327</v>
+        <v>0.004775081777544429</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,34 +5941,34 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.09647585325795509</v>
+        <v>-0.005175350483898725</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.2064653313402128</v>
+        <v>-0.007684800934455589</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.06589399325275033</v>
+        <v>0.005333050702997568</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02284350358122393</v>
+        <v>-0.001587936869929065</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,16 +5977,16 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.2533758204255192</v>
+        <v>0.0003922601057528295</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.09357056407618662</v>
+        <v>-0.001229377758693755</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,16 +5995,16 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1430763525418063</v>
+        <v>-0.004392035580330648</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.06625778218301732</v>
+        <v>0.004696216366769364</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
@@ -6013,16 +6013,16 @@
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1678026449278512</v>
+        <v>-0.003065741548743076</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0290716369076567</v>
+        <v>0.0005962168105079186</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,43 +6031,43 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.2308873496315992</v>
+        <v>0.004745237390250958</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.08509372635130735</v>
+        <v>-0.0002845038795705191</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.2081216822425785</v>
+        <v>0.01011638980960966</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.03643724026298144</v>
+        <v>-0.003755852208250237</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0108468032514815</v>
+        <v>0.0002358617873520248</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,34 +6076,34 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.04187559741933764</v>
+        <v>0.002054036691227916</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.2001523541034005</v>
+        <v>0.0005558471771089392</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.4093546001562924</v>
+        <v>-0.006503077171171242</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
         <v>0</v>
@@ -6112,60 +6112,60 @@
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.3587393255204345</v>
+        <v>-0.002072751090433892</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.3052526313991936</v>
+        <v>-0.2509968048207968</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6339299889530954</v>
+        <v>0.26353735728149</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2295209927449615</v>
+        <v>-0.09358908976969597</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2202146154079925</v>
+        <v>-0.1677382819685606</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5324507487087521</v>
+        <v>0.4175333167121001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4995927265637226</v>
+        <v>-0.143036796172376</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6174,19 +6174,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01928062901122485</v>
+        <v>0.09230373701734874</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3500323973904965</v>
+        <v>0.06700152974805111</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1864118519114296</v>
+        <v>0.04818097275251149</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
@@ -6195,79 +6195,79 @@
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02272493565054422</v>
+        <v>-0.1062825948532376</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2167981033306876</v>
+        <v>-0.1557912655488437</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.1142781167581029</v>
+        <v>-0.2151283887425255</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.1315456380978523</v>
+        <v>-0.005362139542070154</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2577565374688372</v>
+        <v>0.1476418779826818</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.01753022605060512</v>
+        <v>-0.1075891422908701</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.2463246047220774</v>
+        <v>0.04829268005887667</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.7574992817386718</v>
+        <v>0.3011212112335071</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.3648546399273114</v>
+        <v>-0.1611796333640381</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -6282,22 +6282,22 @@
         <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.1937384232392583</v>
+        <v>-0.2179999063266373</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.06074680253556679</v>
+        <v>-0.02177948864408799</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.3903961918688404</v>
+        <v>-0.08850193772013851</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.08405573661782771</v>
+        <v>0.1063083391922777</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1470990857855402</v>
+        <v>0.2374947260967314</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.3906906701199697</v>
+        <v>0.132018705040502</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,49 +6336,49 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.1512665483348841</v>
+        <v>0.0915833443783169</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.4597926369196908</v>
+        <v>0.3978261171855316</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.06781158054042694</v>
+        <v>0.01595773689234282</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.05243362643577967</v>
+        <v>0.08509963327511266</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1313741423994349</v>
+        <v>-0.1075168225388503</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.01125140363454328</v>
+        <v>0.02611395324978637</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
         <v>-0</v>
@@ -6390,46 +6390,46 @@
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.322860009621037</v>
+        <v>-0.09999837924035168</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.1337433074226779</v>
+        <v>-0.2604387720231803</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.3736498237784419</v>
+        <v>0.06810778932096911</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.02276285422062202</v>
+        <v>0.06500807993688165</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1446369394842138</v>
+        <v>-0.1074939581937341</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01403406617051066</v>
+        <v>0.001457104552625561</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6444,22 +6444,22 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.300453368529279</v>
+        <v>0.04756101087138626</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.4905065118504928</v>
+        <v>-0.2996691333025666</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05110760234141163</v>
+        <v>-0.02570601538561641</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.1749519459340669</v>
+        <v>-0.03700273767553934</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.2126695704243778</v>
+        <v>-0.03004962941501907</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
@@ -6483,10 +6483,10 @@
         <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.06316403812488366</v>
+        <v>0.05335160441778366</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
@@ -6495,49 +6495,49 @@
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0.05511221292927963</v>
+        <v>0.1281698978179679</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1267343695114707</v>
+        <v>0.1020608145854295</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.1143816675463318</v>
+        <v>-0.04150690777377403</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.08605449433607222</v>
+        <v>-0.01118498626387742</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.181209347925702</v>
+        <v>0.01700905324151232</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.009019342813549004</v>
+        <v>-0.03043238444356726</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
@@ -6552,19 +6552,19 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>-0.03718476025415313</v>
+        <v>-0.01983555004251581</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1017025126660425</v>
+        <v>-0.1337963381758125</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.02855165235294854</v>
+        <v>-0.119571214959586</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6573,109 +6573,109 @@
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.04849822123289153</v>
+        <v>0.06929644841586609</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1297630275369616</v>
+        <v>-0.1471516490454704</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.05533569400167784</v>
+        <v>-0.01544207265146481</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.192121765754151</v>
+        <v>0.05330129057635517</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.09211553154906796</v>
+        <v>0.01041019227819783</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.09092359573032466</v>
+        <v>0.0407679488749201</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0.01446011860425461</v>
+        <v>-0.09544712068514148</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.03237792684535286</v>
+        <v>0.02670748657703889</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01291698820847831</v>
+        <v>0.05058269356220444</v>
       </c>
       <c r="FU11" t="n">
         <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.08156205300527614</v>
+        <v>0.03898944153886489</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.1830566777509739</v>
+        <v>-0.09715000634697663</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,34 +6692,34 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6233272425654103</v>
+        <v>0.05985070269070766</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3141189483150281</v>
+        <v>-0.1425470351897473</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3450006354070933</v>
+        <v>-0.1138118427659817</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4377578480166519</v>
+        <v>0.09878966906702107</v>
       </c>
       <c r="L12" t="n">
         <v>-0</v>
@@ -6728,13 +6728,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3328071142632696</v>
+        <v>-0.1718309077509252</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2881738188557555</v>
+        <v>-0.1527439761101895</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6746,22 +6746,22 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2069069794435566</v>
+        <v>0.09705259949806046</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
         <v>-0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2117076974661315</v>
+        <v>-0.003058160493547837</v>
       </c>
       <c r="X12" t="n">
         <v>-0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.0301421727889174</v>
+        <v>0.03350785572544989</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
@@ -6773,34 +6773,34 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2477399723218143</v>
+        <v>-0.08144398030359828</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>-0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05842286900360059</v>
+        <v>-0.1767864266856505</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.03682187056296536</v>
+        <v>0.04416849325338892</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.07222457206245804</v>
+        <v>0.1498321761901373</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
@@ -6809,16 +6809,16 @@
         <v>-0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.006841474410709776</v>
+        <v>0.03319746485289313</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.08006017135218756</v>
+        <v>0.02449741481202409</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.6549088414164453</v>
+        <v>0.2605211215540964</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,16 +6836,16 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.0219652668784288</v>
+        <v>-0.0005504473273125572</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.1842782797784158</v>
+        <v>0.001959611832572821</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
@@ -6854,22 +6854,22 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1202588698135653</v>
+        <v>-0.141862253464327</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1386157373931558</v>
+        <v>-0.1515284299167656</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.1463344270210362</v>
+        <v>-0.03616542316373558</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -6878,10 +6878,10 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1298622899040367</v>
+        <v>-0.02462792943109347</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -6890,13 +6890,13 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.2431616570116835</v>
+        <v>0.08019604579480134</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.02736372763433995</v>
+        <v>0.08260406908373308</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,34 +6908,34 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2740356398820328</v>
+        <v>0.2336280028762382</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.03309106637306988</v>
+        <v>-0.01882286603982113</v>
       </c>
       <c r="BZ12" t="n">
         <v>-0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0.07542482844522717</v>
+        <v>-0.001182762689773304</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1592266500607768</v>
+        <v>-0.03132263244149235</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
@@ -6944,13 +6944,13 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.05612087589702432</v>
+        <v>0.04947066970916781</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0791016063372</v>
+        <v>0.01517396029097562</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6959,25 +6959,25 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.2452682562865022</v>
+        <v>-0.1205954269135291</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1568607283425592</v>
+        <v>0.09739599849107078</v>
       </c>
       <c r="CR12" t="n">
         <v>0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0.004983897603303566</v>
+        <v>-0.1002549629488874</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,10 +6986,10 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1251547595983434</v>
+        <v>-0.03274917119497693</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
@@ -6998,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.04871008264462076</v>
+        <v>0.04896051955039667</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.07351840303936252</v>
+        <v>0.02863968118836177</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7013,37 +7013,37 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.3626682143882013</v>
+        <v>-0.0789319194734857</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.03359699895948875</v>
+        <v>-0.002756031122086513</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0.09406716613775946</v>
+        <v>-0.04904087467347263</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06626756986811398</v>
+        <v>-0.002144378273781776</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
@@ -7052,67 +7052,67 @@
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.05797945813252981</v>
+        <v>0.08048965988520157</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0.02038591417358633</v>
+        <v>0.02130429371301442</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1705982653097012</v>
+        <v>0.0405988561027846</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.06580040032335306</v>
+        <v>-0.06183768222272953</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.002275511456605975</v>
+        <v>-0.01761342067528537</v>
       </c>
       <c r="ED12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.04230798882255116</v>
+        <v>-0.006927027107113983</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.08839618321713059</v>
+        <v>0.01070221749587784</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.09586355622593863</v>
+        <v>-0.02225374749371192</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7121,10 +7121,10 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.06907705741091888</v>
+        <v>-0.02283147837910865</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
@@ -7133,25 +7133,25 @@
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.03742095971196316</v>
+        <v>-0.0185830713534077</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0.004496922298665264</v>
+        <v>-0.07870400323976022</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1376596177917514</v>
+        <v>-0.02923914066739704</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
@@ -7160,13 +7160,13 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.05171259208458065</v>
+        <v>0.03502901760477548</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0719848358938327</v>
+        <v>0.01529347885764374</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,25 +7175,25 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02911575073669125</v>
+        <v>-0.03064983595850072</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.1152940741533139</v>
+        <v>-0.005013913509402159</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.06593500169011619</v>
+        <v>-0.02351136843896101</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
@@ -7205,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.008416567614344605</v>
+        <v>-0.01696939177233812</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,28 +7214,28 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01527848234985654</v>
+        <v>-0.002765786606137412</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.00931381775846068</v>
+        <v>0.05057361601616889</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.1211258966109932</v>
+        <v>-0.08474108024135543</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7247,13 +7247,13 @@
         <v>-0</v>
       </c>
       <c r="GE12" t="n">
-        <v>-0.02687541319639537</v>
+        <v>0.05252730293048625</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>1.024972505382257</v>
+        <v>1.392258819633182</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3511377513169431</v>
+        <v>-0.7483931198489243</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5278470127949866</v>
+        <v>-0.3929360768931424</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7669457709385006</v>
+        <v>1.88432831580632</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,25 +7297,25 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3500340443024298</v>
+        <v>-0.9335471706618024</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.4898629447211578</v>
+        <v>-0.4561629433349391</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3087307865701762</v>
+        <v>0.3883597032108612</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
@@ -7324,34 +7324,34 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03651105594204258</v>
+        <v>-0.1485224205125756</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.09468951455221505</v>
+        <v>-0.2169208466592738</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3431419288313772</v>
+        <v>0.08223995432906446</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.09504969845608763</v>
+        <v>-0.4494968051777798</v>
       </c>
       <c r="AG13" t="n">
         <v>-0</v>
@@ -7360,52 +7360,52 @@
         <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.03199682594288976</v>
+        <v>-0.08622799304486915</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1787105022546429</v>
+        <v>0.7088039755675913</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.002002343820584037</v>
+        <v>0.3630599251310345</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.03817298649120922</v>
+        <v>-0.06487206977595719</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.9501960188037181</v>
+        <v>2.043060303597997</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.07541337939820995</v>
+        <v>-0.1537673786139434</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7414,25 +7414,25 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.2978685892114537</v>
+        <v>-0.03783192709752944</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1380117447041011</v>
+        <v>-0.3745978705902072</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.298961956203452</v>
+        <v>-0.6000290362657557</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -7441,70 +7441,70 @@
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.2164063461458012</v>
+        <v>-0.1276189573221204</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1146746272045463</v>
+        <v>0.07889187707045538</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.3849635514058635</v>
+        <v>0.3617212789719595</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0.01930213888111602</v>
+        <v>0.1962395039218043</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.5628297975148089</v>
+        <v>1.351751012634218</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0787867676309482</v>
+        <v>-0.2263939915486319</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0.1114099009112657</v>
+        <v>-0.2616776622473653</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.229549841097109</v>
+        <v>-0.6456873502910159</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
@@ -7513,34 +7513,34 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.01464123852476682</v>
+        <v>0.1666889347041085</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.1658225534714116</v>
+        <v>0.1341655199458948</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.3099232573917902</v>
+        <v>-1.258184066470504</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.2982532066523036</v>
+        <v>0.2162869418093193</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
@@ -7552,49 +7552,49 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.06324279687198262</v>
+        <v>-0.009110113370347558</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1979721869477692</v>
+        <v>-0.6071241679690746</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.02332878148375667</v>
+        <v>0.1103960667076948</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.128476895852236</v>
+        <v>0.1719952109555631</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.5146773210041986</v>
+        <v>-0.538092425665846</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1185580592590236</v>
+        <v>-0.08003760688533489</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7606,22 +7606,22 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.02687870415910539</v>
+        <v>-0.09960959645033698</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.1314607924624603</v>
+        <v>-0.2871565659070961</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01513048523197253</v>
+        <v>0.223736797986226</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7630,16 +7630,16 @@
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0.02485654770335514</v>
+        <v>-0.2537602743456759</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1671326050867656</v>
+        <v>0.5417290388948623</v>
       </c>
       <c r="DY13" t="n">
         <v>-0</v>
@@ -7648,79 +7648,79 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.08174399202466791</v>
+        <v>-0.1662874867673392</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0175626054250582</v>
+        <v>0.3838505989551882</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02363652084842552</v>
+        <v>-0.2337165669882471</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.05379830167694476</v>
+        <v>-0.06135869982391943</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.2181028495913925</v>
+        <v>0.0761382458236854</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1402505414597407</v>
+        <v>-0.3681735547678875</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.02827179400995532</v>
+        <v>-0.02186011546263041</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.02585623760623415</v>
+        <v>0.1187263391371237</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.2277647752194859</v>
+        <v>-0.7122873787272609</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
@@ -7729,25 +7729,25 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.002323848327599822</v>
+        <v>0.09569639242431176</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.1190080377813645</v>
+        <v>0.1769760291805397</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.1090866770028764</v>
+        <v>-0.2553879399339279</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.09325554892777353</v>
+        <v>-0.04567744240243198</v>
       </c>
       <c r="FL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.1302730159578485</v>
+        <v>-0.2097476543975564</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01304875146824822</v>
+        <v>-0.04100312929690685</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,46 +7783,46 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01145042288042497</v>
+        <v>0.08181315174841522</v>
       </c>
       <c r="FU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.04039758136782594</v>
+        <v>-0.05948587252495734</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.2438869435153269</v>
+        <v>-0.3801999124123732</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0.05942325822669611</v>
+        <v>0.1497477386431365</v>
       </c>
     </row>
     <row r="14">
@@ -8396,28 +8396,28 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2917791447199819</v>
+        <v>0.4498072535709137</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.09659102802064227</v>
+        <v>-0.1096963033412778</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1488436280726693</v>
+        <v>-0.4392664385503162</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8426,25 +8426,25 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2195811948985459</v>
+        <v>0.7029604120429506</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.05610464473224834</v>
+        <v>-0.08275955853755733</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1971558997490328</v>
+        <v>-0.4368500639607381</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -8453,97 +8453,97 @@
         <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.07056614395015651</v>
+        <v>0.1622216475329541</v>
       </c>
       <c r="U15" t="n">
-        <v>0.004662397774925435</v>
+        <v>0.09961280841035561</v>
       </c>
       <c r="V15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.007952321558101142</v>
+        <v>0.09186261548452354</v>
       </c>
       <c r="X15" t="n">
         <v>-0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.09735190194413715</v>
+        <v>-0.03097967507759326</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.01308721469816153</v>
+        <v>-0.2114271900652997</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.007753222188768296</v>
+        <v>-0.1289467587353197</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.08443070023770997</v>
+        <v>0.3011690261265372</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.002959237270708554</v>
+        <v>0.0361775366781333</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.02984375967161149</v>
+        <v>0.1704164662224834</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT15" t="n">
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2562777550632507</v>
+        <v>0.6626703106212823</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.0665177820009293</v>
+        <v>0.218362071760346</v>
       </c>
       <c r="AW15" t="n">
         <v>-0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.005728344423768481</v>
+        <v>0.02104574905362568</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -8552,28 +8552,28 @@
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.03079187008431277</v>
+        <v>-0.3622779833906308</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.04653873771606384</v>
+        <v>-0.2216155253261308</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1576075772036674</v>
+        <v>-0.4877440138345697</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
@@ -8588,22 +8588,22 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.05978330948294158</v>
+        <v>0.07399851409426871</v>
       </c>
       <c r="BN15" t="n">
-        <v>-0.02628905341576143</v>
+        <v>-0.01080805417833384</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.07971734591137487</v>
+        <v>0.1195744081119186</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
@@ -8615,52 +8615,52 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1347538674937447</v>
+        <v>0.5692881889526924</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0.06769494944545131</v>
+        <v>0.105519394374233</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.00982834317156733</v>
+        <v>0.009765788548859844</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
         <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.05096081710179302</v>
+        <v>-0.2361391637091354</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.007279672879984789</v>
+        <v>0.03613762752556068</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.02894610524908307</v>
+        <v>0.1117618189548071</v>
       </c>
       <c r="CI15" t="n">
         <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
         <v>-0</v>
@@ -8669,16 +8669,16 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.03543702663229011</v>
+        <v>-0.3866681541643472</v>
       </c>
       <c r="CO15" t="n">
-        <v>-0.004082435416427574</v>
+        <v>-0.01934142474401804</v>
       </c>
       <c r="CP15" t="n">
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.01267159484859716</v>
+        <v>0.1367008449903972</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
@@ -8690,22 +8690,22 @@
         <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.03388117787035383</v>
+        <v>-0.2101395063083046</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0.000159807685859587</v>
+        <v>0.04142279781839796</v>
       </c>
       <c r="CY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.01635978018883025</v>
+        <v>0.07465497195402614</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8720,19 +8720,19 @@
         <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.05559471372939284</v>
+        <v>-0.1485990464569309</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0.0004000776498675392</v>
+        <v>-0.0293301519923652</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.01926051769849174</v>
+        <v>0.02713554252960375</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
@@ -8744,25 +8744,25 @@
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.01636712195776535</v>
+        <v>-0.1035458813395991</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.001283778571662292</v>
+        <v>-0.06121686226687004</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01488696827888524</v>
+        <v>0.1489918464181486</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
@@ -8774,22 +8774,22 @@
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.0207355287767412</v>
+        <v>0.3231905013485707</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0.009300089446034219</v>
+        <v>0.0426420779696406</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.006235462524617879</v>
+        <v>-0.2429317406110215</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8801,25 +8801,25 @@
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.009396011099826114</v>
+        <v>-0.07737203808672072</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0.005001954380826972</v>
+        <v>-0.0373703128505533</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.05086126494596227</v>
+        <v>0.03643772411585949</v>
       </c>
       <c r="EK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
@@ -8828,55 +8828,55 @@
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.01936659079282355</v>
+        <v>-0.149105130713861</v>
       </c>
       <c r="EQ15" t="n">
-        <v>-0.04534204315976578</v>
+        <v>-0.09758135622560636</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.04104036668983279</v>
+        <v>-0.02179129921951996</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
         <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.04053624957012082</v>
+        <v>-0.2394236717681444</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.004474031886710229</v>
+        <v>0.02539563257210931</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.03061319508403231</v>
+        <v>0.07706343769715901</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
@@ -8885,19 +8885,19 @@
         <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.03576088084029022</v>
+        <v>0.08077991650708914</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0.03051623856007338</v>
+        <v>-0.2201654374315043</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.05717478813119291</v>
+        <v>-0.1783094903905371</v>
       </c>
       <c r="FL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
@@ -8906,49 +8906,49 @@
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.000170748093561786</v>
+        <v>0.00132366789202603</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.01577406727397453</v>
+        <v>0.03355494584079499</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.002401510648538843</v>
+        <v>0.0316795249284335</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.01352725690314371</v>
+        <v>-0.2063270143607185</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.02415760502236224</v>
+        <v>-0.1136536633093027</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
         <v>-0</v>
@@ -8957,7 +8957,7 @@
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>0</v>
